--- a/myapp/src/main/resources/Listado_Obra_C.xlsx
+++ b/myapp/src/main/resources/Listado_Obra_C.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\App_TecnoMat\app_lectorArchivos\myapp\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D437DC7D-DDCB-4EF0-B69A-C292D59B29F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1552A4A-1E95-40CE-A834-B4475C083F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4785" yWindow="2820" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Listado" sheetId="1" r:id="rId1"/>
@@ -231,9 +231,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="\O\T0"/>
+    <numFmt numFmtId="164" formatCode="\O\T0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,6 +289,14 @@
       <sz val="10"/>
       <name val="Helv"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -310,7 +318,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -465,24 +473,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -498,11 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -530,7 +516,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -581,7 +567,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -598,14 +583,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -620,9 +610,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -925,1129 +914,1481 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="26"/>
-    </row>
-    <row r="2" spans="1:13" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="47" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="8"/>
+      <c r="M1" s="24"/>
+    </row>
+    <row r="2" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="27"/>
-    </row>
-    <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="27"/>
-    </row>
-    <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="12" t="s">
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="8"/>
+      <c r="M2" s="25"/>
+    </row>
+    <row r="3" spans="1:15" ht="18" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="23"/>
+      <c r="M3" s="25"/>
+    </row>
+    <row r="4" spans="1:15" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="27"/>
-    </row>
-    <row r="5" spans="1:13" ht="36" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="12" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="M4" s="25"/>
+    </row>
+    <row r="5" spans="1:15" ht="36" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="44" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="44"/>
-      <c r="L5" s="1" t="s">
+      <c r="K5" s="42"/>
+      <c r="L5" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="M5" s="40"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="12" t="s">
+      <c r="M5" s="38"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="45" t="s">
+      <c r="E6" s="41"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="45"/>
-      <c r="L6" s="41">
+      <c r="K6" s="43"/>
+      <c r="L6" s="39">
         <v>46065</v>
       </c>
-      <c r="M6" s="42"/>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="46" t="s">
+      <c r="M6" s="40"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="46"/>
-      <c r="L7" s="41">
+      <c r="K7" s="44"/>
+      <c r="L7" s="39">
         <v>46072</v>
       </c>
-      <c r="M7" s="42"/>
-    </row>
-    <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="27"/>
-    </row>
-    <row r="9" spans="1:13" ht="24" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="M7" s="40"/>
+    </row>
+    <row r="8" spans="1:15" ht="18" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="35"/>
+      <c r="M8" s="25"/>
+    </row>
+    <row r="9" spans="1:15" ht="24" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="32"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
         <v>76666</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="23">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
+      <c r="E10" s="21">
+        <v>1</v>
+      </c>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45"/>
+      <c r="M10" s="45"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
         <v>76665</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="23">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
+      <c r="E11" s="21">
+        <v>1</v>
+      </c>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
+      <c r="O11" s="46"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
         <v>75884</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="19">
         <v>607287</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="23">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
+      <c r="E12" s="21">
+        <v>1</v>
+      </c>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
         <v>73809</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="19">
         <v>534017</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="21">
         <v>4</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="21">
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
         <v>65794</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="19">
         <v>550290</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="23">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="21" t="s">
+      <c r="E14" s="21">
+        <v>1</v>
+      </c>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45"/>
+      <c r="M14" s="45"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="23">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="21">
+      <c r="E15" s="21">
+        <v>1</v>
+      </c>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
         <v>79562</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="21">
+      <c r="B16" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="19">
         <v>5818</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="21">
         <v>4</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="21">
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
         <v>79563</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="21">
+      <c r="B17" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="19">
         <v>13302</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="21">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="21">
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
         <v>79564</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="21">
+      <c r="B18" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="19">
         <v>20051</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="21">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="21">
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
         <v>71109</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="21">
+      <c r="B19" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="19">
         <v>20119</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="21">
+      <c r="E19" s="21">
+        <v>1</v>
+      </c>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="45"/>
+      <c r="M19" s="45"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
         <v>80696</v>
       </c>
-      <c r="B20" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="21">
+      <c r="B20" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="19">
         <v>20139</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="21">
+      <c r="E20" s="21">
+        <v>1</v>
+      </c>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
         <v>80697</v>
       </c>
-      <c r="B21" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="21">
+      <c r="B21" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="19">
         <v>20149</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="21">
+      <c r="E21" s="21">
+        <v>1</v>
+      </c>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45"/>
+      <c r="M21" s="45"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
         <v>80698</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="21">
+      <c r="B22" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="19">
         <v>20169</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="21">
+      <c r="E22" s="21">
+        <v>1</v>
+      </c>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="45"/>
+      <c r="M22" s="45"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
         <v>79672</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="21">
+      <c r="B23" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="19">
         <v>20201</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="21">
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
         <v>80699</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="21">
+      <c r="B24" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="19">
         <v>20204</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="21">
+      <c r="E24" s="21">
+        <v>1</v>
+      </c>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
         <v>80700</v>
       </c>
-      <c r="B25" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="21">
+      <c r="B25" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="19">
         <v>20207</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="21">
+      <c r="E25" s="21">
+        <v>1</v>
+      </c>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
         <v>80701</v>
       </c>
-      <c r="B26" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="21">
+      <c r="B26" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="19">
         <v>20211</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="21">
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
         <v>80702</v>
       </c>
-      <c r="B27" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="21">
+      <c r="B27" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="19">
         <v>20279</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="21">
+      <c r="E27" s="21">
+        <v>1</v>
+      </c>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="19">
         <v>79565</v>
       </c>
-      <c r="B28" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="21">
+      <c r="B28" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="19">
         <v>20291</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="21">
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="19">
         <v>79671</v>
       </c>
-      <c r="B29" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="21">
+      <c r="B29" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="19">
         <v>20300</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="21">
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="45"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="19">
         <v>80703</v>
       </c>
-      <c r="B30" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="21">
+      <c r="B30" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="19">
         <v>20307</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="21">
+      <c r="E30" s="21">
+        <v>1</v>
+      </c>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="45"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="19">
         <v>80704</v>
       </c>
-      <c r="B31" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="21">
+      <c r="B31" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="19">
         <v>20310</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="21">
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="45"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="19">
         <v>79845</v>
       </c>
-      <c r="B32" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="21">
+      <c r="B32" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="19">
         <v>20342</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="21">
+      <c r="E32" s="21">
+        <v>1</v>
+      </c>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="45"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="19">
         <v>80705</v>
       </c>
-      <c r="B33" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="21">
+      <c r="B33" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="19">
         <v>20343</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="21">
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="45"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="19">
         <v>79582</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="21">
+      <c r="B34" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="19">
         <v>26088</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="21">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="21">
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45"/>
+      <c r="M34" s="45"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="19">
         <v>79670</v>
       </c>
-      <c r="B35" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="21">
+      <c r="B35" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="19">
         <v>26092</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="21">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="21">
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="45"/>
+      <c r="M35" s="45"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="19">
         <v>79583</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="21">
+      <c r="B36" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="19">
         <v>26093</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="21">
+      <c r="E36" s="21">
+        <v>1</v>
+      </c>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45"/>
+      <c r="M36" s="45"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="19">
         <v>79584</v>
       </c>
-      <c r="B37" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37" s="21">
+      <c r="B37" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="19">
         <v>26249</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E37" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="21">
+      <c r="E37" s="21">
+        <v>1</v>
+      </c>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45"/>
+      <c r="M37" s="45"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="19">
         <v>79585</v>
       </c>
-      <c r="B38" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38" s="21">
+      <c r="B38" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="19">
         <v>26662</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E38" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="21">
+      <c r="E38" s="21">
+        <v>1</v>
+      </c>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="45"/>
+      <c r="M38" s="45"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="19">
         <v>71525</v>
       </c>
-      <c r="B39" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="21">
+      <c r="B39" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="19">
         <v>37310</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="D39" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="21">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="21">
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="45"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="19">
         <v>79587</v>
       </c>
-      <c r="B40" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="21">
+      <c r="B40" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="19">
         <v>37385</v>
       </c>
-      <c r="D40" s="22" t="s">
+      <c r="D40" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="21">
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="19">
         <v>79588</v>
       </c>
-      <c r="B41" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" s="21">
+      <c r="B41" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="19">
         <v>37419</v>
       </c>
-      <c r="D41" s="22" t="s">
+      <c r="D41" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="21">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="21">
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="45"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="19">
         <v>79589</v>
       </c>
-      <c r="B42" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="21">
+      <c r="B42" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="19">
         <v>37438</v>
       </c>
-      <c r="D42" s="22" t="s">
+      <c r="D42" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E42" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="21">
+      <c r="E42" s="21">
+        <v>1</v>
+      </c>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="19">
         <v>79590</v>
       </c>
-      <c r="B43" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43" s="21">
+      <c r="B43" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="19">
         <v>405226</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="21">
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="45"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="45"/>
+      <c r="L43" s="45"/>
+      <c r="M43" s="45"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="19">
         <v>70806</v>
       </c>
-      <c r="B44" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C44" s="21">
+      <c r="B44" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="19">
         <v>407752</v>
       </c>
-      <c r="D44" s="22" t="s">
+      <c r="D44" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="21">
+      <c r="E44" s="21">
+        <v>1</v>
+      </c>
+      <c r="F44" s="45"/>
+      <c r="G44" s="45"/>
+      <c r="H44" s="45"/>
+      <c r="I44" s="45"/>
+      <c r="J44" s="45"/>
+      <c r="K44" s="45"/>
+      <c r="L44" s="45"/>
+      <c r="M44" s="45"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="19">
         <v>79597</v>
       </c>
-      <c r="B45" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="21">
+      <c r="B45" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="19">
         <v>411504</v>
       </c>
-      <c r="D45" s="22" t="s">
+      <c r="D45" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E45" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="21">
+      <c r="E45" s="21">
+        <v>1</v>
+      </c>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="45"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="45"/>
+      <c r="M45" s="45"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="19">
         <v>80707</v>
       </c>
-      <c r="B46" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="21">
+      <c r="B46" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="19">
         <v>420012</v>
       </c>
-      <c r="D46" s="22" t="s">
+      <c r="D46" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E46" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="21">
+      <c r="E46" s="21">
+        <v>1</v>
+      </c>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="45"/>
+      <c r="M46" s="45"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="19">
         <v>80708</v>
       </c>
-      <c r="B47" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="21">
+      <c r="B47" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="19">
         <v>420013</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="D47" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="21">
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="45"/>
+      <c r="M47" s="45"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="19">
         <v>67464</v>
       </c>
-      <c r="B48" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C48" s="21">
+      <c r="B48" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="19">
         <v>420016</v>
       </c>
-      <c r="D48" s="22" t="s">
+      <c r="D48" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E48" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="21">
+      <c r="E48" s="21">
+        <v>1</v>
+      </c>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45"/>
+      <c r="M48" s="45"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="19">
         <v>79603</v>
       </c>
-      <c r="B49" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C49" s="21">
+      <c r="B49" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="19">
         <v>421016</v>
       </c>
-      <c r="D49" s="22" t="s">
+      <c r="D49" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E49" s="23">
+      <c r="E49" s="21">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="21">
+      <c r="F49" s="45"/>
+      <c r="G49" s="45"/>
+      <c r="H49" s="45"/>
+      <c r="I49" s="45"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="45"/>
+      <c r="M49" s="45"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="19">
         <v>79668</v>
       </c>
-      <c r="B50" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="21">
+      <c r="B50" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="19">
         <v>421071</v>
       </c>
-      <c r="D50" s="22" t="s">
+      <c r="D50" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="23">
+      <c r="E50" s="21">
         <v>4</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="21">
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
+      <c r="M50" s="45"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="19">
         <v>79597</v>
       </c>
-      <c r="B51" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C51" s="21">
+      <c r="B51" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="19">
         <v>411504</v>
       </c>
-      <c r="D51" s="22" t="s">
+      <c r="D51" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E51" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="21">
+      <c r="E51" s="21">
+        <v>1</v>
+      </c>
+      <c r="F51" s="45"/>
+      <c r="G51" s="45"/>
+      <c r="H51" s="45"/>
+      <c r="I51" s="45"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="45"/>
+      <c r="M51" s="45"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="19">
         <v>79592</v>
       </c>
-      <c r="B52" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52" s="21">
+      <c r="B52" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="19">
         <v>407800</v>
       </c>
-      <c r="D52" s="22" t="s">
+      <c r="D52" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53" s="21" t="s">
+      <c r="E52" s="21">
+        <v>1</v>
+      </c>
+      <c r="F52" s="45"/>
+      <c r="G52" s="45"/>
+      <c r="H52" s="45"/>
+      <c r="I52" s="45"/>
+      <c r="J52" s="45"/>
+      <c r="K52" s="45"/>
+      <c r="L52" s="45"/>
+      <c r="M52" s="45"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="19"/>
+      <c r="B53" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D53" s="22" t="s">
+      <c r="D53" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E53" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="21">
+      <c r="E53" s="21">
+        <v>1</v>
+      </c>
+      <c r="F53" s="45"/>
+      <c r="G53" s="45"/>
+      <c r="H53" s="45"/>
+      <c r="I53" s="45"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="45"/>
+      <c r="M53" s="45"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="19">
         <v>79562</v>
       </c>
-      <c r="B54" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="21">
+      <c r="B54" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="19">
         <v>5818</v>
       </c>
-      <c r="D54" s="22" t="s">
+      <c r="D54" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E54" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="21">
+      <c r="E54" s="21">
+        <v>1</v>
+      </c>
+      <c r="F54" s="45"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="45"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="45"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="19">
         <v>79563</v>
       </c>
-      <c r="B55" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C55" s="21">
+      <c r="B55" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="19">
         <v>13302</v>
       </c>
-      <c r="D55" s="22" t="s">
+      <c r="D55" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E55" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="21">
+      <c r="E55" s="21">
+        <v>1</v>
+      </c>
+      <c r="F55" s="45"/>
+      <c r="G55" s="45"/>
+      <c r="H55" s="45"/>
+      <c r="I55" s="45"/>
+      <c r="J55" s="45"/>
+      <c r="K55" s="45"/>
+      <c r="L55" s="45"/>
+      <c r="M55" s="45"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="19">
         <v>79582</v>
       </c>
-      <c r="B56" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C56" s="21">
+      <c r="B56" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="19">
         <v>26088</v>
       </c>
-      <c r="D56" s="22" t="s">
+      <c r="D56" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E56" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="21">
+      <c r="E56" s="21">
+        <v>1</v>
+      </c>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="45"/>
+      <c r="J56" s="45"/>
+      <c r="K56" s="45"/>
+      <c r="L56" s="45"/>
+      <c r="M56" s="45"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="19">
         <v>79583</v>
       </c>
-      <c r="B57" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" s="21">
+      <c r="B57" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="19">
         <v>26093</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D57" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E57" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="21">
+      <c r="E57" s="21">
+        <v>1</v>
+      </c>
+      <c r="F57" s="45"/>
+      <c r="G57" s="45"/>
+      <c r="H57" s="45"/>
+      <c r="I57" s="45"/>
+      <c r="J57" s="45"/>
+      <c r="K57" s="45"/>
+      <c r="L57" s="45"/>
+      <c r="M57" s="45"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="19">
         <v>80709</v>
       </c>
-      <c r="B58" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C58" s="21">
+      <c r="B58" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="19">
         <v>420279</v>
       </c>
-      <c r="D58" s="22" t="s">
+      <c r="D58" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="E58" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="21">
+      <c r="E58" s="21">
+        <v>1</v>
+      </c>
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="45"/>
+      <c r="I58" s="45"/>
+      <c r="J58" s="45"/>
+      <c r="K58" s="45"/>
+      <c r="L58" s="45"/>
+      <c r="M58" s="45"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="19">
         <v>79603</v>
       </c>
-      <c r="B59" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C59" s="21">
+      <c r="B59" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="19">
         <v>421016</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="D59" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E59" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="21">
+      <c r="E59" s="21">
+        <v>1</v>
+      </c>
+      <c r="F59" s="45"/>
+      <c r="G59" s="45"/>
+      <c r="H59" s="45"/>
+      <c r="I59" s="45"/>
+      <c r="J59" s="45"/>
+      <c r="K59" s="45"/>
+      <c r="L59" s="45"/>
+      <c r="M59" s="45"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="19">
         <v>79604</v>
       </c>
-      <c r="B60" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60" s="21">
+      <c r="B60" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" s="19">
         <v>421072</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="E60" s="23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="21">
+      <c r="E60" s="21">
+        <v>1</v>
+      </c>
+      <c r="F60" s="45"/>
+      <c r="G60" s="45"/>
+      <c r="H60" s="45"/>
+      <c r="I60" s="45"/>
+      <c r="J60" s="45"/>
+      <c r="K60" s="45"/>
+      <c r="L60" s="45"/>
+      <c r="M60" s="45"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="19">
         <v>79584</v>
       </c>
-      <c r="B61" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C61" s="21">
+      <c r="B61" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="19">
         <v>26249</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="D61" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E61" s="23">
+      <c r="E61" s="21">
         <v>2</v>
       </c>
+      <c r="F61" s="45"/>
+      <c r="G61" s="45"/>
+      <c r="H61" s="45"/>
+      <c r="I61" s="45"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="45"/>
+      <c r="L61" s="45"/>
+      <c r="M61" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="8">
